--- a/Result/profitability/3252.xlsx
+++ b/Result/profitability/3252.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>-0.09250000000000003</v>
       </c>
       <c r="N2" t="n">
-        <v>32.18875</v>
+        <v>33.7975</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-2.51</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3775</v>
+        <v>-0.395</v>
       </c>
       <c r="N3" t="n">
-        <v>24.44375</v>
+        <v>25.08375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.96</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.48625</v>
+        <v>-0.525</v>
       </c>
       <c r="N4" t="n">
-        <v>12.32625</v>
+        <v>12.97125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.66</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.57875</v>
+        <v>-0.60375</v>
       </c>
       <c r="N5" t="n">
-        <v>-11.46</v>
+        <v>-10.8475</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5887500000000001</v>
+        <v>-0.5987500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-14.615</v>
+        <v>-13.56875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.35</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.61375</v>
+        <v>-0.67125</v>
       </c>
       <c r="N7" t="n">
-        <v>-20.1725</v>
+        <v>-20.1325</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.67375</v>
+        <v>-0.71375</v>
       </c>
       <c r="N8" t="n">
-        <v>-23.42125</v>
+        <v>-23.05</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3252</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>114</v>
+      </c>
+      <c r="D75" t="n">
+        <v>65</v>
+      </c>
+      <c r="E75" t="n">
+        <v>50</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="G75" t="n">
+        <v>7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.04125000000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>38.46625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3.555555555555556</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.969999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.07340583292140379</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.899999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1271736309369322</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
